--- a/data/output/flags/flag_report.xlsx
+++ b/data/output/flags/flag_report.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$H$102</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$J$137</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H102"/>
+  <dimension ref="A1:J137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -446,8 +446,10 @@
     <col width="23" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="23" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -483,12 +485,22 @@
       </c>
       <c r="G1" s="2" t="inlineStr">
         <is>
-          <t>suggestion</t>
+          <t>current_value</t>
         </is>
       </c>
       <c r="H1" s="2" t="inlineStr">
         <is>
+          <t>expected</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
           <t>severity</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>recommendation</t>
         </is>
       </c>
     </row>
@@ -851,7 +863,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -874,7 +886,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -897,7 +909,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -920,7 +932,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -1093,7 +1105,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -1116,7 +1128,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -1139,7 +1151,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -1162,7 +1174,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -1185,7 +1197,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -1208,7 +1220,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -1231,7 +1243,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -1254,7 +1266,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -1277,7 +1289,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -1300,7 +1312,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -1323,7 +1335,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -1346,7 +1358,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -1369,7 +1381,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -1392,7 +1404,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -1415,7 +1427,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -1438,7 +1450,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -1461,7 +1473,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -1484,7 +1496,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -1507,7 +1519,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -1530,7 +1542,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -1553,7 +1565,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -1576,7 +1588,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -1599,7 +1611,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -1622,7 +1634,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -1645,7 +1657,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -1668,7 +1680,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -1691,7 +1703,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
@@ -1714,7 +1726,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -1737,7 +1749,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
@@ -1760,7 +1772,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
@@ -1783,7 +1795,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
@@ -1806,7 +1818,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
@@ -1829,7 +1841,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
@@ -1852,7 +1864,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
@@ -1875,7 +1887,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
@@ -1898,7 +1910,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
@@ -1921,7 +1933,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
@@ -1944,7 +1956,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
@@ -1967,7 +1979,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
@@ -1990,7 +2002,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
@@ -2013,7 +2025,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
@@ -2036,7 +2048,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
@@ -2059,7 +2071,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
@@ -2082,7 +2094,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
@@ -2105,7 +2117,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
@@ -2128,7 +2140,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
@@ -2151,7 +2163,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
@@ -2174,7 +2186,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
@@ -2197,7 +2209,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
@@ -2220,7 +2232,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
@@ -2243,7 +2255,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
@@ -2266,7 +2278,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
@@ -2289,7 +2301,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
@@ -2312,7 +2324,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
@@ -2335,7 +2347,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
@@ -2358,7 +2370,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
@@ -2381,7 +2393,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
@@ -2404,7 +2416,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
@@ -2427,7 +2439,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
@@ -2450,7 +2462,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
@@ -2473,7 +2485,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
@@ -2496,7 +2508,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
@@ -2519,7 +2531,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
@@ -2542,7 +2554,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
@@ -2563,8 +2575,813 @@
         </is>
       </c>
     </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>407</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>place_type</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Missing place_type</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>406</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>PlaceTypeRule</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>408</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>place_type</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Missing place_type</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>407</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>PlaceTypeRule</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>409</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>place_type</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Missing place_type</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>408</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>PlaceTypeRule</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>410</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>place_type</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Missing place_type</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>409</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>PlaceTypeRule</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>411</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>place_type</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Missing place_type</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>410</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>PlaceTypeRule</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>412</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>place_type</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Missing place_type</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>411</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>PlaceTypeRule</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>413</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>place_type</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Missing place_type</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>412</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>PlaceTypeRule</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>414</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>place_type</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Missing place_type</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>413</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>PlaceTypeRule</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>415</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>place_type</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Missing place_type</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>414</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>PlaceTypeRule</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>407</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>marital_status</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Missing marital_status</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>406</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>MaritalStatusRule</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>408</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>marital_status</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Missing marital_status</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>407</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>MaritalStatusRule</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>409</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>marital_status</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Missing marital_status</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>408</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>MaritalStatusRule</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>410</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>marital_status</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Missing marital_status</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>409</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>MaritalStatusRule</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>411</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>marital_status</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Missing marital_status</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>410</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>MaritalStatusRule</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>412</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>marital_status</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Missing marital_status</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>411</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>MaritalStatusRule</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>413</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>marital_status</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Missing marital_status</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>412</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>MaritalStatusRule</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>414</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>marital_status</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Missing marital_status</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>413</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>MaritalStatusRule</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>415</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>marital_status</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Missing marital_status</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>414</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>MaritalStatusRule</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>407</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>nationality</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Missing nationality</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>406</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>NationalityRule</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>408</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>nationality</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Missing nationality</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>407</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>NationalityRule</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>409</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>nationality</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Missing nationality</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>408</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>NationalityRule</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>410</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>nationality</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Missing nationality</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>409</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>NationalityRule</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>411</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>nationality</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Missing nationality</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>410</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>NationalityRule</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>412</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>nationality</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Missing nationality</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>411</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>NationalityRule</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>413</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>nationality</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Missing nationality</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>412</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>NationalityRule</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>414</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>nationality</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Missing nationality</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>413</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>NationalityRule</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>407</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Missing education</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>406</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>EducationRule</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>408</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Missing education</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>407</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>EducationRule</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>409</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Missing education</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>408</v>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>EducationRule</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>410</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Missing education</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>409</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>EducationRule</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>411</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Missing education</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>410</v>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>EducationRule</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>412</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Missing education</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>411</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>EducationRule</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>413</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Missing education</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>412</v>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>EducationRule</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>414</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Missing education</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>413</v>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>EducationRule</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>415</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Missing education</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>414</v>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>EducationRule</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H102"/>
+  <autoFilter ref="A1:J137"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/output/flags/flag_report.xlsx
+++ b/data/output/flags/flag_report.xlsx
@@ -4226,7 +4226,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Missing sex</t>
+          <t>Missing Sex</t>
         </is>
       </c>
       <c r="E154" t="n">
@@ -4249,7 +4249,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Missing sex</t>
+          <t>Missing Sex</t>
         </is>
       </c>
       <c r="E155" t="n">
@@ -4272,7 +4272,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Missing sex</t>
+          <t>Missing Sex</t>
         </is>
       </c>
       <c r="E156" t="n">
@@ -4295,7 +4295,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Missing sex</t>
+          <t>Missing Sex</t>
         </is>
       </c>
       <c r="E157" t="n">
@@ -4318,7 +4318,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Missing sex</t>
+          <t>Missing Sex</t>
         </is>
       </c>
       <c r="E158" t="n">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Missing sex</t>
+          <t>Missing Sex</t>
         </is>
       </c>
       <c r="E159" t="n">
@@ -4364,7 +4364,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Missing sex</t>
+          <t>Missing Sex</t>
         </is>
       </c>
       <c r="E160" t="n">
@@ -4387,7 +4387,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Missing sex</t>
+          <t>Missing Sex</t>
         </is>
       </c>
       <c r="E161" t="n">
@@ -4410,7 +4410,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Missing sex</t>
+          <t>Missing Sex</t>
         </is>
       </c>
       <c r="E162" t="n">
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Missing sex</t>
+          <t>Missing Sex</t>
         </is>
       </c>
       <c r="E163" t="n">
@@ -4456,7 +4456,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Missing nature_of_birth</t>
+          <t>Missing Nature of Birth</t>
         </is>
       </c>
       <c r="E164" t="n">
@@ -4479,7 +4479,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Missing nature_of_birth</t>
+          <t>Missing Nature of Birth</t>
         </is>
       </c>
       <c r="E165" t="n">
@@ -4502,7 +4502,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Missing nature_of_birth</t>
+          <t>Missing Nature of Birth</t>
         </is>
       </c>
       <c r="E166" t="n">
@@ -4525,7 +4525,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Missing nature_of_birth</t>
+          <t>Missing Nature of Birth</t>
         </is>
       </c>
       <c r="E167" t="n">
@@ -4548,7 +4548,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Missing nature_of_birth</t>
+          <t>Missing Nature of Birth</t>
         </is>
       </c>
       <c r="E168" t="n">
@@ -4571,7 +4571,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Missing nature_of_birth</t>
+          <t>Missing Nature of Birth</t>
         </is>
       </c>
       <c r="E169" t="n">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Missing nature_of_birth</t>
+          <t>Missing Nature of Birth</t>
         </is>
       </c>
       <c r="E170" t="n">
@@ -4617,7 +4617,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Missing nature_of_birth</t>
+          <t>Missing Nature of Birth</t>
         </is>
       </c>
       <c r="E171" t="n">
@@ -4640,7 +4640,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Missing nature_of_birth</t>
+          <t>Missing Nature of Birth</t>
         </is>
       </c>
       <c r="E172" t="n">
@@ -4663,7 +4663,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Missing birth_weight</t>
+          <t>Missing Birth Weight</t>
         </is>
       </c>
       <c r="E173" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Missing birth_weight</t>
+          <t>Missing Birth Weight</t>
         </is>
       </c>
       <c r="E174" t="n">
@@ -4709,7 +4709,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Missing birth_weight</t>
+          <t>Missing Birth Weight</t>
         </is>
       </c>
       <c r="E175" t="n">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Missing birth_weight</t>
+          <t>Missing Birth Weight</t>
         </is>
       </c>
       <c r="E176" t="n">
@@ -4755,7 +4755,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Missing birth_weight</t>
+          <t>Missing Birth Weight</t>
         </is>
       </c>
       <c r="E177" t="n">
@@ -4778,7 +4778,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Missing birth_weight</t>
+          <t>Missing Birth Weight</t>
         </is>
       </c>
       <c r="E178" t="n">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Missing birth_weight</t>
+          <t>Missing Birth Weight</t>
         </is>
       </c>
       <c r="E179" t="n">
@@ -4824,7 +4824,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Missing birth_weight</t>
+          <t>Missing Birth Weight</t>
         </is>
       </c>
       <c r="E180" t="n">
@@ -4847,7 +4847,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Missing birth_weight</t>
+          <t>Missing Birth Weight</t>
         </is>
       </c>
       <c r="E181" t="n">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Missing mother_age</t>
+          <t>Missing Mother Age</t>
         </is>
       </c>
       <c r="E182" t="n">
@@ -4893,7 +4893,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Missing mother_age</t>
+          <t>Missing Mother Age</t>
         </is>
       </c>
       <c r="E183" t="n">
@@ -4916,7 +4916,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Missing mother_age</t>
+          <t>Missing Mother Age</t>
         </is>
       </c>
       <c r="E184" t="n">
@@ -4939,7 +4939,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Missing mother_age</t>
+          <t>Missing Mother Age</t>
         </is>
       </c>
       <c r="E185" t="n">
@@ -4962,7 +4962,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Missing mother_age</t>
+          <t>Missing Mother Age</t>
         </is>
       </c>
       <c r="E186" t="n">
@@ -4985,7 +4985,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Missing mother_age</t>
+          <t>Missing Mother Age</t>
         </is>
       </c>
       <c r="E187" t="n">
@@ -5008,7 +5008,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Missing mother_age</t>
+          <t>Missing Mother Age</t>
         </is>
       </c>
       <c r="E188" t="n">
@@ -5031,7 +5031,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Missing mother_age</t>
+          <t>Missing Mother Age</t>
         </is>
       </c>
       <c r="E189" t="n">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Missing mother_age</t>
+          <t>Missing Mother Age</t>
         </is>
       </c>
       <c r="E190" t="n">
